--- a/outputs/41969.xlsx
+++ b/outputs/41969.xlsx
@@ -155,19 +155,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
